--- a/pensum/ol17/OL17_Klasseoppgaver_v5.xlsx
+++ b/pensum/ol17/OL17_Klasseoppgaver_v5.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="157">
   <si>
     <t xml:space="preserve">Klasseoppgaver til Organisasjon og ledelse kapittel 17: Ledelse og motivasjon (V5)</t>
   </si>
@@ -149,9 +149,18 @@
     <t xml:space="preserve">a)  Hvor mange prosent av uka på 37,5 timer bruker Ronny på å montere selv? Én desimal.</t>
   </si>
   <si>
+    <t xml:space="preserve">Formel og begrep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andel av uka = timer på aktiviteten / timer i uka × 100. Begrepet bak er lederen på operativt nivå som «den første blant likemenn» (Organisasjon og ledelse 17.1).</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Boka sier at rollene lederen vanskelig kommer utenom i det daglige, er ressursfordeler, overvåker og informasjonsformidler (17.3). Hvor mange timer i Ronnys uke går til disse tre rollene til sammen?</t>
   </si>
   <si>
+    <t xml:space="preserve">Mintzbergs roller: ressursfordeler (beslutningsrolle), overvåker og informasjonsformidler (informasjonsroller). De tre er rollene lederen vanskelig kommer utenom i det daglige (Organisasjon og ledelse 17.3, 17.3.2–17.3.3).</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Hvilken av disse tre rollene hos Adizes får ingen egne timer i Ronnys uke?   A: Produsenten   B: Administratoren   C: Integratoren   (skriv bokstaven)</t>
   </si>
   <si>
@@ -176,6 +185,24 @@
     <t xml:space="preserve">e)  Kari spør om Ronny kan ta solcelle og lading i tillegg, slik at han får 9 under seg. Hva sier uka hans om det, og hva bør Ronny endre hvis han får avdelingen? Tre–fire setninger med minst ett tall.</t>
   </si>
   <si>
+    <t xml:space="preserve">Ingen ny formel. Bruk tidsbruken (17.3), Adizes' roller (17.3), delegering som lederegenskap (tabell 17.1) og kontrollspennet (kap. 14.2).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hint, hvis du står fast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tallene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andelen: 15 delt på 37,5. De tre rollene: hvilken linje er å fordele (ressursfordeler), å følge med (overvåker) og å fortelle videre (informasjonsformidler)? Legg sammen timene.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rollene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adizes: produsenten får jobben gjort, administratoren har rutiner og kontroll, integratoren bygger team. Finn en linje i uka for hver. Hvilken finner du ikke?</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 17, avsnitt 17.2 (lederoppgaver), 17.3 (Adizes' fire roller, Mintzbergs roller, rollene lederen ikke kommer utenom, tidsbruk) og 17.4 (tabell 17.1, delegering). Ronnys lag: OL11 og appen. Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -263,6 +290,21 @@
     <t xml:space="preserve">e)  Mona sier: «Jeg er demokratisk. Jeg liker ikke å bestemme over folk.» Hvordan bør hun lede lærlingen og de to montørene de første ukene etter at lærlingen har begynt, og hva betyr utsagnet hennes? Tre–fire setninger.</t>
   </si>
   <si>
+    <t xml:space="preserve">Ingen ny formel. Bruk skalaen demokratisk–autoritær (17.5.1–17.5.2) og situasjonsbestemt ledelse med Hersey og Blanchard (17.5.3, figur 17.3).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modenheten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spør to ting om hver person i hver oppgave: kan hun eller han det (kompetanse)? Vil hun eller han det (motivasjon)? Begge nei: instruerende. Vil, men kan ikke: overtalende.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Én person, to oppgaver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montør 1 har to oppgaver. Er han like moden i begge? Boka sier at situasjonen også avhenger av om oppgaven er kjent eller ny. For e: les 17.5.2 om skalaen demokratisk–autoritær.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 17, avsnitt 17.5.1–17.5.2 (demokratisk og autoritær lederstil som ytterpunkter), 17.5.3 (situasjonsvariablene, modenhetsnivå, Hersey og Blanchards fire lederstiler, figur 17.3). Fjell Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -314,6 +356,9 @@
     <t xml:space="preserve">a)  Hva koster alle åtte forslagene til sammen, og hvor mye mer er det enn potten?</t>
   </si>
   <si>
+    <t xml:space="preserve">Ingen formel fra boka; dette er en sum og en differanse. Begrepet bak er knappe ressurser, som lederen som ressursfordeler må prioritere (Organisasjon og ledelse 17.3.3).</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Ja eller nei: er forslaget en motivasjonsfaktor hos Herzberg (17.8.3)? Nei betyr at det er en hygienefaktor.</t>
   </si>
   <si>
@@ -338,12 +383,30 @@
     <t xml:space="preserve">c)  Hvor mange prosent av potten på 150 000 kr koster de forslagene du sorterte som motivasjonsfaktorer i b) til sammen?</t>
   </si>
   <si>
+    <t xml:space="preserve">Andel av potten = kroner til tiltakene / potten × 100. Motivasjonsfaktorene etter Herzberg (Organisasjon og ledelse 17.8.3).</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Tom sier: «Gi alle lønnstillegg, så trives de.» Hva sier Herzbergs undersøkelse?   A: Tom har rett: høy lønn gir trivsel   B: Lønn er uviktig og kan droppes   C: God lønn fjerner mistrivsel, men skaper ikke trivsel   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  Sett sammen en pakke innenfor 150 000 kr, og begrunn den med Herzberg og Maslow. Si hva den koster og hvor stor del av potten den tar, og hvilket forslag du forkaster. Tre–fire setninger.</t>
   </si>
   <si>
+    <t xml:space="preserve">Ingen ny formel. Bruk Herzberg (17.8.3), Maslow med ytre og indre belønning (17.8.1, behovskategoriene i kap. 2, figur 2.1) og eventuelt McGregor (17.8.2).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summen og sorteringen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legg sammen alle åtte. Sorter så: ligger tiltaket i selve arbeidet (ansvar, anerkjennelse, utvikling), eller rundt arbeidet (lønn, goder, lokaler, kolleger)?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prosenten og Tom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legg sammen kronene for forslagene du sa ja til i b), og del på 150 000. Noen av dem koster ingenting. Til Tom: hva skjer hvis lønna er lav? Hva skjer hvis den er høy? Det er to forskjellige svar.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 17, avsnitt 17.8.1 (Maslow, ytre og indre belønning), 17.8.2 (McGregor) og 17.8.3 (Herzbergs motivasjons- og hygienefaktorer). Potten er fra appens Vurdering 1 og øvingsheftet, forslagene er tilpasset. Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -401,9 +464,15 @@
     <t xml:space="preserve">a)  Hvor mange prosent av en montørs 1 800 betalte timer faktureres i dag? Én desimal.</t>
   </si>
   <si>
+    <t xml:space="preserve">Faktureringsgrad = fakturerbare timer / betalte timer × 100. Timetallene er fra Fjell-casen (OK02). Målstyring er standardisering av resultater (Organisasjon og ledelse 17.9.3).</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Hvor mange kroner mer i året fakturerer Fjell hvis begge montørene når 1 500 timer?</t>
   </si>
   <si>
+    <t xml:space="preserve">Økt fakturering = antall montører × økning i timer × timepris. Timeprisen 890 kr er Fjells (OK02).</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Boka sier at mål må være klare og tydelige, realistiske, kjente og aksepterte, og innbyrdes i samsvar (17.9.3). Hvilket krav er svakest ivaretatt når Mona skrev målet på tavla uten å snakke med montørene?   A: Klare og tydelige   B: Kjente og aksepterte   C: Realistiske   (skriv bokstaven)</t>
   </si>
   <si>
@@ -411,6 +480,18 @@
   </si>
   <si>
     <t xml:space="preserve">e)  Hvordan bør Mona styre Fjell etter dette? Si hva som bør målstyres, hva som bør regelstyres, og hva hun gjør med målet på tavla. Bruk minst to av bokas styringsformer. Tre–fire setninger.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingen ny formel. Bruk styringsformene i 17.9.1–17.9.5 og kravene til mål i 17.9.3.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faktureringsgrad: 1 400 delt på 1 800. Målet: 100 timer mer per montør, to montører, 890 kr timen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kravene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les de fire kravene i 17.9.3 og spør: har montørene fått si ja til målet? Henger timemålet sammen med sjekklista og kurset, eller går det på bekostning av dem?</t>
   </si>
   <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 17, avsnitt 17.9 (styring), 17.9.1–17.9.5 (direkte styring, regelstyring, målstyring med fire krav, standardisering av kunnskap og normer). Suboptimalisering: kap. 14. Timetallene: Fjell_Elektro_fakta.md og OK02. Fjell Elektro AS er en konstruert casebedrift.</t>
@@ -424,7 +505,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.##;\−#,##0.##;\0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -491,8 +572,30 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF2F4A6D"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -514,7 +617,25 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF4F6FA"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFEEF2F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF2F8"/>
+        <bgColor rgb="FFF4F6FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8954A"/>
+        <bgColor rgb="FF808080"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBF6EA"/>
+        <bgColor rgb="FFF4F6FA"/>
       </patternFill>
     </fill>
   </fills>
@@ -567,7 +688,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="33">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -656,11 +777,31 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -709,8 +850,8 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFF4F6FA"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFFBF6EA"/>
+      <rgbColor rgb="FFEEF2F8"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -724,7 +865,7 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFF4F6FA"/>
       <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
@@ -738,7 +879,7 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF5E6670"/>
-      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FFB8954A"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
@@ -1041,7 +1182,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1207,33 +1348,18 @@
         <v/>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
+    <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="21" t="str">
-        <f aca="false">IF(F20="","",IF(ABS(F20-(12.5))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
+      <c r="B20" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="22"/>
-      <c r="G21" s="21" t="str">
-        <f aca="false">IF(F21="","",IF(UPPER(TRIM(F21))="C","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
+      <c r="C20" s="23"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="23"/>
+      <c r="G20" s="23"/>
     </row>
     <row r="22" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
@@ -1243,154 +1369,251 @@
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="s">
+      <c r="F22" s="12"/>
+      <c r="G22" s="21" t="str">
+        <f aca="false">IF(F22="","",IF(ABS(F22-(12.5))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="21" t="str">
-        <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="s">
+      <c r="C23" s="23"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="23"/>
+    </row>
+    <row r="25" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7" t="s">
         <v>45</v>
-      </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="21" t="str">
-        <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="s">
-        <v>46</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
-      <c r="F25" s="22"/>
+      <c r="F25" s="24"/>
       <c r="G25" s="21" t="str">
-        <f aca="false">IF(F25="","",IF(UPPER(TRIM(F25))="JA","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F25="","",IF(UPPER(TRIM(F25))="C","Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="21" t="str">
-        <f aca="false">IF(F26="","",IF(UPPER(TRIM(F26))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
       <c r="E27" s="7"/>
-      <c r="F27" s="22"/>
+      <c r="F27" s="24"/>
       <c r="G27" s="21" t="str">
-        <f aca="false">IF(F27="","",IF(UPPER(TRIM(F27))="NEI","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F27="","",IF(UPPER(TRIM(F27))="JA","Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="23"/>
-      <c r="B29" s="23"/>
-      <c r="C29" s="23"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="23"/>
-      <c r="F29" s="23"/>
-      <c r="G29" s="23"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="23"/>
-      <c r="B30" s="23"/>
-      <c r="C30" s="23"/>
-      <c r="D30" s="23"/>
-      <c r="E30" s="23"/>
-      <c r="F30" s="23"/>
-      <c r="G30" s="23"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="23"/>
-      <c r="B31" s="23"/>
-      <c r="C31" s="23"/>
-      <c r="D31" s="23"/>
-      <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
-      <c r="G31" s="23"/>
-    </row>
-    <row r="33" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
+      <c r="F28" s="24"/>
+      <c r="G28" s="21" t="str">
+        <f aca="false">IF(F28="","",IF(UPPER(TRIM(F28))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="24"/>
+      <c r="G29" s="21" t="str">
+        <f aca="false">IF(F29="","",IF(UPPER(TRIM(F29))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="6" t="s">
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="24"/>
+      <c r="G30" s="21" t="str">
+        <f aca="false">IF(F30="","",IF(UPPER(TRIM(F30))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B34" s="6"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="21" t="str">
+        <f aca="false">IF(F31="","",IF(UPPER(TRIM(F31))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="25"/>
+      <c r="B33" s="25"/>
+      <c r="C33" s="25"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="25"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="25"/>
+      <c r="B34" s="25"/>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="25"/>
+      <c r="B35" s="25"/>
+      <c r="C35" s="25"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="25"/>
+      <c r="F35" s="25"/>
+      <c r="G35" s="25"/>
+    </row>
+    <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="C36" s="23"/>
+      <c r="D36" s="23"/>
+      <c r="E36" s="23"/>
+      <c r="F36" s="23"/>
+      <c r="G36" s="23"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="B39" s="26"/>
+      <c r="C39" s="26"/>
+      <c r="D39" s="26"/>
+      <c r="E39" s="26"/>
+      <c r="F39" s="26"/>
+      <c r="G39" s="26"/>
+    </row>
+    <row r="40" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="B40" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="C40" s="28"/>
+      <c r="D40" s="28"/>
+      <c r="E40" s="28"/>
+      <c r="F40" s="28"/>
+      <c r="G40" s="28"/>
+    </row>
+    <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="B41" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="C41" s="28"/>
+      <c r="D41" s="28"/>
+      <c r="E41" s="28"/>
+      <c r="F41" s="28"/>
+      <c r="G41" s="28"/>
+    </row>
+    <row r="43" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="6"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="23">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A16:G16"/>
     <mergeCell ref="A18:E18"/>
     <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="B20:G20"/>
     <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="B23:G23"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A27:E27"/>
     <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A29:G31"/>
-    <mergeCell ref="A33:G33"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A33:G35"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="B40:G40"/>
+    <mergeCell ref="B41:G41"/>
+    <mergeCell ref="A43:G43"/>
+    <mergeCell ref="A44:G44"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1407,7 +1630,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1418,7 +1641,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1428,7 +1651,7 @@
     </row>
     <row r="4" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1439,7 +1662,7 @@
     </row>
     <row r="5" customFormat="false" ht="138.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1450,10 +1673,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="20" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C7" s="20"/>
       <c r="D7" s="20"/>
@@ -1462,11 +1685,11 @@
       <c r="G7" s="20"/>
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="24" t="s">
-        <v>57</v>
+      <c r="A8" s="29" t="s">
+        <v>66</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -1475,11 +1698,11 @@
       <c r="G8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="24" t="s">
-        <v>59</v>
+      <c r="A9" s="29" t="s">
+        <v>68</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -1488,11 +1711,11 @@
       <c r="G9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="24" t="s">
-        <v>61</v>
+      <c r="A10" s="29" t="s">
+        <v>70</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -1501,11 +1724,11 @@
       <c r="G10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="24" t="s">
-        <v>63</v>
+      <c r="A11" s="29" t="s">
+        <v>72</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -1514,11 +1737,11 @@
       <c r="G11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="24" t="s">
-        <v>65</v>
+      <c r="A12" s="29" t="s">
+        <v>74</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -1527,11 +1750,11 @@
       <c r="G12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="24" t="s">
-        <v>67</v>
+      <c r="A13" s="29" t="s">
+        <v>76</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -1556,13 +1779,13 @@
     </row>
     <row r="16" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
-      <c r="F16" s="22"/>
+      <c r="F16" s="24"/>
       <c r="G16" s="21" t="str">
         <f aca="false">IF(F16="","",IF(UPPER(TRIM(F16))="B","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1570,13 +1793,13 @@
     </row>
     <row r="17" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
-      <c r="F17" s="22"/>
+      <c r="F17" s="24"/>
       <c r="G17" s="21" t="str">
         <f aca="false">IF(F17="","",IF(UPPER(TRIM(F17))="B","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1584,7 +1807,7 @@
     </row>
     <row r="18" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -1593,13 +1816,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
-      <c r="F19" s="22"/>
+      <c r="F19" s="24"/>
       <c r="G19" s="21" t="str">
         <f aca="false">IF(F19="","",IF(UPPER(TRIM(F19))="JA","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1607,13 +1830,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
-      <c r="F20" s="22"/>
+      <c r="F20" s="24"/>
       <c r="G20" s="21" t="str">
         <f aca="false">IF(F20="","",IF(UPPER(TRIM(F20))="NEI","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1621,13 +1844,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
-      <c r="F21" s="22"/>
+      <c r="F21" s="24"/>
       <c r="G21" s="21" t="str">
         <f aca="false">IF(F21="","",IF(UPPER(TRIM(F21))="JA","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1635,13 +1858,13 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
-      <c r="F22" s="22"/>
+      <c r="F22" s="24"/>
       <c r="G22" s="21" t="str">
         <f aca="false">IF(F22="","",IF(UPPER(TRIM(F22))="JA","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1649,13 +1872,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
-      <c r="F23" s="22"/>
+      <c r="F23" s="24"/>
       <c r="G23" s="21" t="str">
         <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="NEI","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1663,13 +1886,13 @@
     </row>
     <row r="24" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
-      <c r="F24" s="22"/>
+      <c r="F24" s="24"/>
       <c r="G24" s="21" t="str">
         <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="B","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1677,7 +1900,7 @@
     </row>
     <row r="25" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -1685,56 +1908,106 @@
       <c r="E25" s="7"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="23"/>
-      <c r="B26" s="23"/>
-      <c r="C26" s="23"/>
-      <c r="D26" s="23"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="23"/>
-      <c r="G26" s="23"/>
+      <c r="A26" s="25"/>
+      <c r="B26" s="25"/>
+      <c r="C26" s="25"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="25"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="23"/>
-      <c r="B27" s="23"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
+      <c r="A27" s="25"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="23"/>
-      <c r="B28" s="23"/>
-      <c r="C28" s="23"/>
-      <c r="D28" s="23"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="23"/>
-    </row>
-    <row r="30" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
+      <c r="A28" s="25"/>
+      <c r="B28" s="25"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="25"/>
+    </row>
+    <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="C29" s="23"/>
+      <c r="D29" s="23"/>
+      <c r="E29" s="23"/>
+      <c r="F29" s="23"/>
+      <c r="G29" s="23"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="B32" s="26"/>
+      <c r="C32" s="26"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="26"/>
+      <c r="G32" s="26"/>
+    </row>
+    <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="B33" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="C33" s="28"/>
+      <c r="D33" s="28"/>
+      <c r="E33" s="28"/>
+      <c r="F33" s="28"/>
+      <c r="G33" s="28"/>
+    </row>
+    <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="B34" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="C34" s="28"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="28"/>
+      <c r="F34" s="28"/>
+      <c r="G34" s="28"/>
+    </row>
+    <row r="36" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="27">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -1756,8 +2029,12 @@
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A26:G28"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="B29:G29"/>
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A37:G37"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1774,7 +2051,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1785,7 +2062,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1795,7 +2072,7 @@
     </row>
     <row r="4" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1806,7 +2083,7 @@
     </row>
     <row r="5" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1817,18 +2094,18 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="B8" s="11" t="n">
         <v>70000</v>
@@ -1837,7 +2114,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="B9" s="14" t="n">
         <v>48000</v>
@@ -1846,7 +2123,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="B10" s="11" t="n">
         <v>35000</v>
@@ -1855,7 +2132,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="B11" s="14" t="n">
         <v>0</v>
@@ -1864,7 +2141,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="B12" s="11" t="n">
         <v>60000</v>
@@ -1873,7 +2150,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="B13" s="14" t="n">
         <v>0</v>
@@ -1882,7 +2159,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="B14" s="11" t="n">
         <v>45000</v>
@@ -1891,7 +2168,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="B15" s="14" t="n">
         <v>55000</v>
@@ -1899,13 +2176,13 @@
       <c r="C15" s="12"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="25" t="s">
-        <v>94</v>
-      </c>
-      <c r="B16" s="26" t="n">
+      <c r="A16" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="B16" s="31" t="n">
         <v>150000</v>
       </c>
-      <c r="C16" s="27"/>
+      <c r="C16" s="32"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
@@ -1935,7 +2212,7 @@
     </row>
     <row r="20" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -1947,52 +2224,37 @@
         <v/>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="21" t="str">
-        <f aca="false">IF(F22="","",IF(UPPER(TRIM(F22))="NEI","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="C21" s="23"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="23"/>
+    </row>
+    <row r="23" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="21" t="str">
-        <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
-      <c r="F24" s="22"/>
+      <c r="F24" s="24"/>
       <c r="G24" s="21" t="str">
         <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="NEI","Riktig","Prøv igjen"))</f>
         <v/>
@@ -2000,13 +2262,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
-      <c r="F25" s="22"/>
+      <c r="F25" s="24"/>
       <c r="G25" s="21" t="str">
         <f aca="false">IF(F25="","",IF(UPPER(TRIM(F25))="JA","Riktig","Prøv igjen"))</f>
         <v/>
@@ -2014,127 +2276,217 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
-      <c r="F26" s="22"/>
+      <c r="F26" s="24"/>
       <c r="G26" s="21" t="str">
-        <f aca="false">IF(F26="","",IF(UPPER(TRIM(F26))="JA","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F26="","",IF(UPPER(TRIM(F26))="NEI","Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
       <c r="E27" s="7"/>
-      <c r="F27" s="22"/>
+      <c r="F27" s="24"/>
       <c r="G27" s="21" t="str">
-        <f aca="false">IF(F27="","",IF(UPPER(TRIM(F27))="NEI","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F27="","",IF(UPPER(TRIM(F27))="JA","Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
-      <c r="F28" s="12"/>
+      <c r="F28" s="24"/>
       <c r="G28" s="21" t="str">
-        <f aca="false">IF(F28="","",IF(ABS(F28-(32))&lt;=0.1,"Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F28="","",IF(UPPER(TRIM(F28))="JA","Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
       <c r="E29" s="7"/>
-      <c r="F29" s="22"/>
+      <c r="F29" s="24"/>
       <c r="G29" s="21" t="str">
-        <f aca="false">IF(F29="","",IF(UPPER(TRIM(F29))="C","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F29="","",IF(UPPER(TRIM(F29))="NEI","Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="23"/>
-      <c r="B31" s="23"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="21" t="str">
+        <f aca="false">IF(F30="","",IF(ABS(F30-(32))&lt;=0.1,"Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="23" t="s">
+        <v>119</v>
+      </c>
       <c r="C31" s="23"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
       <c r="F31" s="23"/>
       <c r="G31" s="23"/>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="23"/>
-      <c r="B32" s="23"/>
-      <c r="C32" s="23"/>
-      <c r="D32" s="23"/>
-      <c r="E32" s="23"/>
-      <c r="F32" s="23"/>
-      <c r="G32" s="23"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="23"/>
-      <c r="B33" s="23"/>
-      <c r="C33" s="23"/>
-      <c r="D33" s="23"/>
-      <c r="E33" s="23"/>
-      <c r="F33" s="23"/>
-      <c r="G33" s="23"/>
-    </row>
-    <row r="35" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B36" s="6"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
+    <row r="33" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="21" t="str">
+        <f aca="false">IF(F33="","",IF(UPPER(TRIM(F33))="C","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="25"/>
+      <c r="B35" s="25"/>
+      <c r="C35" s="25"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="25"/>
+      <c r="F35" s="25"/>
+      <c r="G35" s="25"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="25"/>
+      <c r="B36" s="25"/>
+      <c r="C36" s="25"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="25"/>
+      <c r="F36" s="25"/>
+      <c r="G36" s="25"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="25"/>
+      <c r="B37" s="25"/>
+      <c r="C37" s="25"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="25"/>
+      <c r="F37" s="25"/>
+      <c r="G37" s="25"/>
+    </row>
+    <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="C38" s="23"/>
+      <c r="D38" s="23"/>
+      <c r="E38" s="23"/>
+      <c r="F38" s="23"/>
+      <c r="G38" s="23"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="B41" s="26"/>
+      <c r="C41" s="26"/>
+      <c r="D41" s="26"/>
+      <c r="E41" s="26"/>
+      <c r="F41" s="26"/>
+      <c r="G41" s="26"/>
+    </row>
+    <row r="42" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="B42" s="28" t="s">
+        <v>124</v>
+      </c>
+      <c r="C42" s="28"/>
+      <c r="D42" s="28"/>
+      <c r="E42" s="28"/>
+      <c r="F42" s="28"/>
+      <c r="G42" s="28"/>
+    </row>
+    <row r="43" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="B43" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="C43" s="28"/>
+      <c r="D43" s="28"/>
+      <c r="E43" s="28"/>
+      <c r="F43" s="28"/>
+      <c r="G43" s="28"/>
+    </row>
+    <row r="45" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="B45" s="6"/>
+      <c r="C45" s="6"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="6"/>
+      <c r="G45" s="6"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B46" s="6"/>
+      <c r="C46" s="6"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="6"/>
+      <c r="G46" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="24">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A17:G17"/>
     <mergeCell ref="A19:E19"/>
     <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="B21:G21"/>
     <mergeCell ref="A23:E23"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A25:E25"/>
@@ -2143,9 +2495,16 @@
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="A29:E29"/>
     <mergeCell ref="A30:E30"/>
-    <mergeCell ref="A31:G33"/>
-    <mergeCell ref="A35:G35"/>
-    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="B31:G31"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A35:G37"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="B42:G42"/>
+    <mergeCell ref="B43:G43"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="A46:G46"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2162,7 +2521,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -2173,7 +2532,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2183,7 +2542,7 @@
     </row>
     <row r="4" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -2194,7 +2553,7 @@
     </row>
     <row r="5" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -2205,10 +2564,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="20" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C7" s="20"/>
       <c r="D7" s="20"/>
@@ -2217,11 +2576,11 @@
       <c r="G7" s="20"/>
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="24" t="s">
-        <v>110</v>
+      <c r="A8" s="29" t="s">
+        <v>131</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -2230,11 +2589,11 @@
       <c r="G8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="24" t="s">
-        <v>112</v>
+      <c r="A9" s="29" t="s">
+        <v>133</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -2243,11 +2602,11 @@
       <c r="G9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="24" t="s">
-        <v>114</v>
+      <c r="A10" s="29" t="s">
+        <v>135</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -2256,11 +2615,11 @@
       <c r="G10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="24" t="s">
-        <v>116</v>
+      <c r="A11" s="29" t="s">
+        <v>137</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -2269,11 +2628,11 @@
       <c r="G11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="24" t="s">
-        <v>118</v>
+      <c r="A12" s="29" t="s">
+        <v>139</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -2282,11 +2641,11 @@
       <c r="G12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="24" t="s">
-        <v>120</v>
+      <c r="A13" s="29" t="s">
+        <v>141</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -2295,11 +2654,11 @@
       <c r="G13" s="7"/>
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="24" t="s">
-        <v>122</v>
+      <c r="A14" s="29" t="s">
+        <v>143</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
@@ -2324,7 +2683,7 @@
     </row>
     <row r="17" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -2336,108 +2695,184 @@
         <v/>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="21" t="str">
-        <f aca="false">IF(F18="","",IF(ABS(F18-(178000))&lt;=1,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="21" t="str">
-        <f aca="false">IF(F19="","",IF(UPPER(TRIM(F19))="B","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="C18" s="23"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="23"/>
+    </row>
+    <row r="20" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
-      <c r="F20" s="22"/>
+      <c r="F20" s="12"/>
       <c r="G20" s="21" t="str">
-        <f aca="false">IF(F20="","",IF(UPPER(TRIM(F20))="B","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F20="","",IF(ABS(F20-(178000))&lt;=1,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="23"/>
-      <c r="B22" s="23"/>
-      <c r="C22" s="23"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="23"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="23"/>
-      <c r="B23" s="23"/>
-      <c r="C23" s="23"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="23"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="23"/>
-      <c r="B24" s="23"/>
-      <c r="C24" s="23"/>
-      <c r="D24" s="23"/>
-      <c r="E24" s="23"/>
-      <c r="F24" s="23"/>
-      <c r="G24" s="23"/>
-    </row>
-    <row r="26" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
+    <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="C21" s="23"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="23"/>
+    </row>
+    <row r="23" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="21" t="str">
+        <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="21" t="str">
+        <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="25"/>
+      <c r="B26" s="25"/>
+      <c r="C26" s="25"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="25"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="25"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="25"/>
+      <c r="B28" s="25"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="25"/>
+    </row>
+    <row r="29" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="C29" s="23"/>
+      <c r="D29" s="23"/>
+      <c r="E29" s="23"/>
+      <c r="F29" s="23"/>
+      <c r="G29" s="23"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="B32" s="26"/>
+      <c r="C32" s="26"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="26"/>
+      <c r="G32" s="26"/>
+    </row>
+    <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="B33" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="C33" s="28"/>
+      <c r="D33" s="28"/>
+      <c r="E33" s="28"/>
+      <c r="F33" s="28"/>
+      <c r="G33" s="28"/>
+    </row>
+    <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="B34" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="C34" s="28"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="28"/>
+      <c r="F34" s="28"/>
+      <c r="G34" s="28"/>
+    </row>
+    <row r="36" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="25">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -2450,13 +2885,19 @@
     <mergeCell ref="B14:G14"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="B18:G18"/>
     <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A22:G24"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A26:G28"/>
+    <mergeCell ref="B29:G29"/>
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A37:G37"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/pensum/ol17/OL17_Klasseoppgaver_v5.xlsx
+++ b/pensum/ol17/OL17_Klasseoppgaver_v5.xlsx
@@ -125,7 +125,7 @@
     <t xml:space="preserve">Morgenmøte med laget</t>
   </si>
   <si>
-    <t xml:space="preserve">Det akutte: syk montør o.l.</t>
+    <t xml:space="preserve">Det akutte: syk montør og lignende</t>
   </si>
   <si>
     <t xml:space="preserve">= Sum uka</t>
@@ -203,7 +203,7 @@
     <t xml:space="preserve">Adizes: produsenten får jobben gjort, administratoren har rutiner og kontroll, integratoren bygger team. Finn en linje i uka for hver. Hvilken finner du ikke?</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 17, avsnitt 17.2 (lederoppgaver), 17.3 (Adizes' fire roller, Mintzbergs roller, rollene lederen ikke kommer utenom, tidsbruk) og 17.4 (tabell 17.1, delegering). Ronnys lag: OL11 og appen. Nordlys Elektro AS er en konstruert casebedrift.</t>
+    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 17, avsnitt 17.2 (lederoppgaver), 17.3 (Adizes' fire roller, Mintzbergs roller, rollene lederen ikke kommer utenom, tidsbruk) og 17.4 (tabell 17.1, delegering). Ronnys lag: kap. 11 og appen. Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
     <t xml:space="preserve">Regnearket er øvingsstøtte. Det kan ikke siteres eller vises til i besvarelser, prosjektoppgaver eller eksamen; der gjelder læreboka og oppgitte primærkilder.</t>
@@ -416,7 +416,7 @@
     <t xml:space="preserve">Kort oppsummert: Styring handler om systemer og prinsipper for beslutningstaking og samordning (17.9). Målstyring er standardisering av resultater: de som utfører arbeidet, vet hva resultatet skal bli, men har en viss styring med virkemiddelbruken (17.9.3). Den legger til rette for desentralisering og fremmer kreativitet og initiativ. Ulempen er at personer kan bli så opptatt av egne delmål at organisasjonens overordnede mål blir skadelidende. Målene må være klare og tydelige, realistiske, kjente og aksepterte, og innbyrdes i samsvar. Regelstyring skaper forutsigbarhet, men hemmer kreativiteten (17.9.2).</t>
   </si>
   <si>
-    <t xml:space="preserve">Fjell Elektro AS er i sitt andre driftsår. En montør har 1 800 betalte timer i året: 1 400 fakturerbare og 400 andre (henting av materiell, kurs, dokumentasjon). Timeprisen er 890 kr uten mva. En mandag skrev Mona på tavla på verkstedet: «Mål: 1 500 fakturerbare timer per montør i år.» Hun snakket ikke med montørene om det først. Etter tre måneder ligger den ene montøren over målet. Samtidig har Mona sett at sjekklista før spenningssetting er hoppet over to ganger, og montør 1 har meldt seg av solcellekurset før Fjells første solcelleanlegg fordi kurstimer ikke er fakturerbare. Gå fram slik: regn faktureringsgraden i dag og hva målet er verdt, finn hvilket krav til mål som er svakest, se hva som har skjedd, og gi Mona et råd om styringen.</t>
+    <t xml:space="preserve">Fjell Elektro AS er i sitt andre driftsår. En montør har 1 800 betalte timer i året: 1 400 fakturerbare og 400 andre (henting av materiell, kurs, dokumentasjon). Timeprisen er 890 kr uten merverdiavgift. En mandag skrev Mona på tavla på verkstedet: «Mål: 1 500 fakturerbare timer per montør i år.» Hun snakket ikke med montørene om det først. Etter tre måneder ligger den ene montøren over målet. Samtidig har Mona sett at sjekklista før spenningssetting er hoppet over to ganger, og montør 1 har meldt seg av solcellekurset før Fjells første solcelleanlegg fordi kurstimer ikke er fakturerbare. Gå fram slik: regn faktureringsgraden i dag og hva målet er verdt, finn hvilket krav til mål som er svakest, se hva som har skjedd, og gi Mona et råd om styringen.</t>
   </si>
   <si>
     <t xml:space="preserve">Betalte timer per montør</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">Timepris</t>
   </si>
   <si>
-    <t xml:space="preserve">890 kr uten mva</t>
+    <t xml:space="preserve">890 kr uten merverdiavgift</t>
   </si>
   <si>
     <t xml:space="preserve">Monas mål</t>
@@ -464,13 +464,13 @@
     <t xml:space="preserve">a)  Hvor mange prosent av en montørs 1 800 betalte timer faktureres i dag? Én desimal.</t>
   </si>
   <si>
-    <t xml:space="preserve">Faktureringsgrad = fakturerbare timer / betalte timer × 100. Timetallene er fra Fjell-casen (OK02). Målstyring er standardisering av resultater (Organisasjon og ledelse 17.9.3).</t>
+    <t xml:space="preserve">Faktureringsgrad = fakturerbare timer / betalte timer × 100. Timetallene er fra Fjell-casen (Økonomistyring kap. 2). Målstyring er standardisering av resultater (Organisasjon og ledelse 17.9.3).</t>
   </si>
   <si>
     <t xml:space="preserve">b)  Hvor mange kroner mer i året fakturerer Fjell hvis begge montørene når 1 500 timer?</t>
   </si>
   <si>
-    <t xml:space="preserve">Økt fakturering = antall montører × økning i timer × timepris. Timeprisen 890 kr er Fjells (OK02).</t>
+    <t xml:space="preserve">Økt fakturering = antall montører × økning i timer × timepris. Timeprisen 890 kr er Fjells (Økonomistyring kap. 2).</t>
   </si>
   <si>
     <t xml:space="preserve">c)  Boka sier at mål må være klare og tydelige, realistiske, kjente og aksepterte, og innbyrdes i samsvar (17.9.3). Hvilket krav er svakest ivaretatt når Mona skrev målet på tavla uten å snakke med montørene?   A: Klare og tydelige   B: Kjente og aksepterte   C: Realistiske   (skriv bokstaven)</t>
@@ -494,7 +494,7 @@
     <t xml:space="preserve">Les de fire kravene i 17.9.3 og spør: har montørene fått si ja til målet? Henger timemålet sammen med sjekklista og kurset, eller går det på bekostning av dem?</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 17, avsnitt 17.9 (styring), 17.9.1–17.9.5 (direkte styring, regelstyring, målstyring med fire krav, standardisering av kunnskap og normer). Suboptimalisering: kap. 14. Timetallene: Fjell_Elektro_fakta.md og OK02. Fjell Elektro AS er en konstruert casebedrift.</t>
+    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 17, avsnitt 17.9 (styring), 17.9.1–17.9.5 (direkte styring, regelstyring, målstyring med fire krav, standardisering av kunnskap og normer). Suboptimalisering: kap. 14. Timetallene: Fjell_Elektro_fakta.md og Økonomistyring kap. 2. Fjell Elektro AS er en konstruert casebedrift.</t>
   </si>
 </sst>
 </file>
@@ -2695,7 +2695,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="22" t="s">
         <v>41</v>
       </c>

--- a/pensum/ol17/OL17_Klasseoppgaver_v5.xlsx
+++ b/pensum/ol17/OL17_Klasseoppgaver_v5.xlsx
@@ -26,7 +26,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="157">
   <si>
-    <t xml:space="preserve">Klasseoppgaver til Organisasjon og ledelse kapittel 17: Ledelse og motivasjon (V5)</t>
+    <t xml:space="preserve">Klasseoppgaver til Organisasjon og ledelse kapittel 17: Ledelse og motivasjon (versjon 5)</t>
   </si>
   <si>
     <t xml:space="preserve">LØM · Fagskolen Oslo, Avdeling Elkraft · versjon 5, oktober 2026</t>

--- a/pensum/ol17/OL17_Klasseoppgaver_v5.xlsx
+++ b/pensum/ol17/OL17_Klasseoppgaver_v5.xlsx
@@ -95,7 +95,7 @@
     <t xml:space="preserve">Kort oppsummert: Lederoppgavene er de samme på alle nivåer: formulere mål, planlegge tiltak, iverksette og gjennomføre, og kontrollere og evaluere, og i tillegg informere, kommunisere og motivere (17.2). Adizes peker på fire roller som en leder eller et lederteam må fylle: produsent, administrator, entreprenør og integrator. Mintzberg deler rollene i interpersonelle roller, informasjonsroller og beslutningsroller; rollene lederen vanskelig kommer utenom i det daglige, er ressursfordeler, overvåker og informasjonsformidler. Synliggjøring og evaluering av tidsbruk kan hjelpe lederen til å prioritere bedre (17.3).</t>
   </si>
   <si>
-    <t xml:space="preserve">Casen er lagt til 2026/2027. Ronny Fjeld er formann for prosjekt og nybygg hos Nordlys og leder 6 montører og 1 lærling. Solcelle og lading har 2 montører og ingen leder. Kari har flere alternativer: å gjøre den mest erfarne solcellemontøren til leder, å la Ronny ta avdelingen i tillegg, slik at han får 9 under seg, å legge den under Tom i service, eller å ansette en leder utenfra. Ronny er det første hun ser nærmere på. Før hun bestemmer seg, ber hun Ronny skrive ned hvor timene går i en vanlig uke på 37,5 timer. Tabellen viser det han skrev. Gå fram slik: regn hvor stor del av uka han monterer selv, finn timene i de tre rollene boka sier lederen ikke kommer utenom, se hvilken av Adizes' roller som mangler, sorter hva som er lederoppgaver, og gi Kari et råd.</t>
+    <t xml:space="preserve">Casen er lagt til 2026/2027. Ronny Fjeld er formann for prosjekt og nybygg hos Nordlys og leder 6 montører og 1 lærling. Solcelle og lading har 2 montører og ingen leder. Kari har flere alternativer: å gjøre den mest erfarne solcellemontøren til leder, å la Ronny ta avdelingen i tillegg, slik at han får 7 + 2 = 9 under seg, å legge den under Tom i service, eller å ansette en leder utenfra. Ronny er det første hun ser nærmere på. Før hun bestemmer seg, ber hun Ronny skrive ned hvor timene går i en vanlig uke på 37,5 timer. Tabellen viser det han skrev. Gå fram slik: regn hvor stor del av uka han monterer selv, finn timene i de tre rollene boka sier lederen ikke kommer utenom, se hvilken av Adizes' roller som mangler, sorter hva som er lederoppgaver, og gi Kari et råd.</t>
   </si>
   <si>
     <t xml:space="preserve">Ronnys uke</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">      Ronny trekker kabel selv fordi det går fortere   (Ja eller Nei)</t>
   </si>
   <si>
-    <t xml:space="preserve">e)  Kari spør om Ronny kan ta solcelle og lading i tillegg, slik at han får 9 under seg. Hva sier uka hans om det, og hva bør Ronny endre hvis han får avdelingen? Tre–fire setninger med minst ett tall.</t>
+    <t xml:space="preserve">e)  Kari spør om Ronny kan ta solcelle og lading i tillegg, slik at han får 7 + 2 = 9 under seg. Hva sier uka hans om det, og hva bør Ronny endre hvis han får avdelingen? Tre–fire setninger med minst ett tall.</t>
   </si>
   <si>
     <t xml:space="preserve">Ingen ny formel. Bruk tidsbruken (17.3), Adizes' roller (17.3), delegering som lederegenskap (tabell 17.1) og kontrollspennet (kap. 14.2).</t>
@@ -1212,7 +1212,7 @@
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
     </row>
-    <row r="5" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
         <v>23</v>
       </c>
